--- a/aq_files/0672.xlsx
+++ b/aq_files/0672.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,888 +413,573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Options (if MCQ)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data mart is:</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Full DW</t>
+          <t>VMs virtualize the entire __________ including hardware.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Subset of DW</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent mart:</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standalone</t>
+          <t>Which component sits between VMs and physical hardware?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>From DW</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>A) Docker Engine B) Hypervisor C) Container Runtime D) Kernel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Independent mart:</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From DW</t>
+          <t>Docker containers share the host's ____________.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Standalone</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Size:</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>True or False: VMs have faster startup time than containers.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) True B) False</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Used by:</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Org-wide</t>
+          <t>What is the primary advantage of containers over VMs in terms of resource usage?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logical mart:</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>A VM includes a full __________ OS per instance.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stores:</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Which has higher overhead: VM or Container?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subject-specific</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Faster than DW:</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Scenario: You need strict security isolation with different kernels. Which should you choose?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Depends</t>
+          <t>A) Docker B) VM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Schema is:</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>Docker containers typically boot in ___________ (seconds/milliseconds).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Structured</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reduces:</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>VMs require a __________ for each guest OS.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data silo:</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Which type of virtualization does Docker use?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>A) Hardware virtualization B) OS-level virtualization C) Para-virtualization D) Full virtualization</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Conformed dimension:</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Scenario: You have 10 microservices each needing 50MB RAM. Which is more efficient?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Random</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Advantage:</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Faster access</t>
+          <t>What is the size difference between a typical VM image and a container image?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Costly</t>
+          <t>A) VM is smaller B) Same size C) Container is smaller</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Example tool:</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>VMs provide __________ isolation compared to containers.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sales team needs only sales KPIs quickly. Choose:</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>True or False: A VM can run a different OS than the host.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Data mart</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>A) True B) False</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finance builds its own standalone analytics store. Type?</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dependent mart</t>
+          <t>Which technology allows containers to be lightweight?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Independent mart</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>A) Namespaces and Cgroups B) Hyper-V C) KVM D) VirtualBox</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lake</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Multiple marts share same customer dimension. Concept?</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Silo</t>
+          <t>What is a major use case for VMs over containers?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Conformed dimension</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cache</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Too many isolated marts causing inconsistency. Issue?</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Scenario: You need to run Windows container on a Linux host. Is this possible?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Data silos</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Throughput</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Need restricted access for department data. Feature?</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Open access</t>
+          <t>Which has faster live migration: VM or Container?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Access control</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Caching</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Replication</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subset derived from enterprise DW for marketing. Type?</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Container images are typically __________ MBs while VMs are __________ GBs.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dependent</t>
+          <t>Two words</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cache</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
